--- a/Result/profitability/9938.xlsx
+++ b/Result/profitability/9938.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,16 +669,16 @@
         <v>0.16</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9487500000000001</v>
+        <v>0.81875</v>
       </c>
       <c r="N2" t="n">
-        <v>34.6925</v>
+        <v>33.615</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7775000000000001</v>
+        <v>0.7225</v>
       </c>
       <c r="N3" t="n">
-        <v>33.37375</v>
+        <v>32.60625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.6512500000000001</v>
+        <v>0.52</v>
       </c>
       <c r="N4" t="n">
-        <v>31.76375</v>
+        <v>30.64</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.48</v>
+        <v>0.4575</v>
       </c>
       <c r="N5" t="n">
-        <v>30.0325</v>
+        <v>29.42</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40375</v>
+        <v>0.32</v>
       </c>
       <c r="N6" t="n">
-        <v>28.86875</v>
+        <v>28.1025</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.27875</v>
+        <v>0.24875</v>
       </c>
       <c r="N7" t="n">
-        <v>27.59625</v>
+        <v>27.36875</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>0.20625</v>
+        <v>0.15875</v>
       </c>
       <c r="N8" t="n">
-        <v>27.28375</v>
+        <v>27.0175</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9938</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3803</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2674</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>381</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>10.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-145</v>
+      </c>
+      <c r="J75" t="n">
+        <v>236</v>
+      </c>
+      <c r="K75" t="n">
+        <v>146</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9900000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>34.52125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.4367816091954023</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.129999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06696007544797233</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.2686567164179106</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.899999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1417004048582996</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
